--- a/stories/arbres/TREE-SEC-014.xlsx
+++ b/stories/arbres/TREE-SEC-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo est dans le train avec Papa. Il y a un panier. Kenzo voit un goûter. Avant de goûter l'inconnu, on demande. On demande à Papa, l'adulte. Les mains attendent. Maman a préparé le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1657,6 +1684,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1873,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
     </row>
@@ -2013,6 +2050,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2199,6 +2241,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2365,6 +2412,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Le train souffle. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2551,6 +2603,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2717,6 +2774,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Un oiseau passe derrière la vitre. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le siège est doux. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. L'eau de la gourde cliquette. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Le panier craque. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3887,6 +3979,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4053,6 +4150,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le siège est doux. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4317,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4488,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. L'eau de la gourde cliquette. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4655,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4826,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. On entend des voix calmes. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4993,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5164,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Un oiseau passe derrière la vitre. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5223,6 +5355,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5389,6 +5526,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5551,6 +5693,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5717,6 +5864,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5879,6 +6031,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6045,6 +6202,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6207,6 +6369,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6373,6 +6540,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6729,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6906,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,6 +7097,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7081,6 +7268,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Le siège est doux. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7267,6 +7459,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7433,6 +7630,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le siège est doux. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7595,6 +7797,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7761,6 +7968,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. L'eau de la gourde cliquette. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7923,6 +8135,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8089,6 +8306,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. On entend des voix calmes. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8251,6 +8473,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8417,6 +8644,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. L'eau de la gourde cliquette. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8603,6 +8835,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8769,6 +9006,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8931,6 +9173,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9097,6 +9344,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9259,6 +9511,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9425,6 +9682,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9587,6 +9849,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9753,6 +10020,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. On entend des voix calmes. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9939,6 +10211,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10105,6 +10382,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. On entend des voix calmes. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10267,6 +10549,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10433,6 +10720,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le train souffle. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10595,6 +10887,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10761,6 +11058,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le panier craque. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10923,6 +11225,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11089,6 +11396,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11273,6 +11585,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
     </row>
@@ -11445,6 +11762,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11631,6 +11953,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11797,6 +12124,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes. Le train souffle. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11983,6 +12315,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12149,6 +12486,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12311,6 +12653,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12477,6 +12824,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12639,6 +12991,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12805,6 +13162,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12967,6 +13329,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13133,6 +13500,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre. Le panier craque. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13319,6 +13691,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13485,6 +13862,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. On entend des voix calmes. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13647,6 +14029,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13813,6 +14200,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le train souffle. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13975,6 +14367,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14141,6 +14538,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Le panier craque. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14303,6 +14705,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14469,6 +14876,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette. Un oiseau passe derrière la vitre. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14655,6 +15067,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14821,6 +15238,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend une pomme. Le train souffle. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14983,6 +15405,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15149,6 +15576,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un yaourt. Le panier craque. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15311,6 +15743,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15477,6 +15914,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo prend un morceau de pain. Un oiseau passe derrière la vitre. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15639,6 +16081,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15657,7 +16104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15674,6 +16121,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-014.xlsx
+++ b/stories/arbres/TREE-SEC-014.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Kenzo est dans le train avec Papa. Il y a un panier. Kenzo voit un goûter. Avant de goûter l'inconnu, on demande. On demande à Papa, l'adulte. Les mains attendent. Maman a préparé le panier.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
           <t>narrateur|Tom est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1880,6 +1888,7 @@
           <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2055,6 +2064,7 @@
           <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2246,6 +2256,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2417,6 +2428,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Le train souffle. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2620,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2792,7 @@
           <t>narrateur|Kenzo prend une pomme. Un oiseau passe derrière la vitre. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3132,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le siège est doux. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3472,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. L'eau de la gourde cliquette. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3812,7 @@
           <t>narrateur|Kenzo a choisi le livre. Le panier craque. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3984,6 +4004,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4155,6 +4176,7 @@
           <t>narrateur|Kenzo prend une pomme. Le siège est doux. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4322,6 +4344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4493,6 +4516,7 @@
           <t>narrateur|Kenzo prend un yaourt. L'eau de la gourde cliquette. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4660,6 +4684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4831,6 +4856,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. On entend des voix calmes. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4998,6 +5024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5169,6 +5196,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Un oiseau passe derrière la vitre. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5360,6 +5388,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5531,6 +5560,7 @@
           <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5698,6 +5728,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5869,6 +5900,7 @@
           <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6036,6 +6068,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6207,6 +6240,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6374,6 +6408,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6545,6 +6580,7 @@
           <t>narrateur|Léa est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6736,6 +6772,7 @@
           <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6911,6 +6948,7 @@
           <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7102,6 +7140,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7273,6 +7312,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Le siège est doux. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7464,6 +7504,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7635,6 +7676,7 @@
           <t>narrateur|Kenzo prend une pomme. Le siège est doux. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7802,6 +7844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7973,6 +8016,7 @@
           <t>narrateur|Kenzo prend un yaourt. L'eau de la gourde cliquette. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8140,6 +8184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8311,6 +8356,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. On entend des voix calmes. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8478,6 +8524,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8649,6 +8696,7 @@
           <t>narrateur|Kenzo a choisi le livre. L'eau de la gourde cliquette. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8840,6 +8888,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9011,6 +9060,7 @@
           <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9178,6 +9228,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9349,6 +9400,7 @@
           <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9516,6 +9568,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9687,6 +9740,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9854,6 +9908,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10025,6 +10080,7 @@
           <t>narrateur|Kenzo a choisi la dînette. On entend des voix calmes. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10216,6 +10272,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10387,6 +10444,7 @@
           <t>narrateur|Kenzo prend une pomme. On entend des voix calmes. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10554,6 +10612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10725,6 +10784,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le train souffle. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10892,6 +10952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11063,6 +11124,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le panier craque. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11230,6 +11292,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11401,6 +11464,7 @@
           <t>narrateur|Sami est dans le même wagon, avec un adulte. Kenzo voit un goûter. Avant de goûter l'inconnu, il demande. Il demande à Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11592,6 +11656,7 @@
           <t>narrateur|On fait quoi ? Demander à l'adulte.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11767,6 +11832,7 @@
           <t>narrateur|Oui. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo retient : demander, inconnu, adulte. Les mains attendent, près de Papa. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11958,6 +12024,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12129,6 +12196,7 @@
           <t>narrateur|Kenzo a choisi les cubes. Le train souffle. Kenzo pose les cubes sur les genoux de Papa. Il demande avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12320,6 +12388,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12491,6 +12560,7 @@
           <t>narrateur|Kenzo prend une pomme. L'eau de la gourde cliquette. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12658,6 +12728,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12829,6 +12900,7 @@
           <t>narrateur|Kenzo prend un yaourt. On entend des voix calmes. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12996,6 +13068,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13167,6 +13240,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le train souffle. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13334,6 +13408,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13505,6 +13580,7 @@
           <t>narrateur|Kenzo a choisi le livre. Le panier craque. Kenzo ouvre le livre. Il demande à l'adulte avant de goûter l'inconnu. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13696,6 +13772,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13867,6 +13944,7 @@
           <t>narrateur|Kenzo prend une pomme. On entend des voix calmes. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14034,6 +14112,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14205,6 +14284,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le train souffle. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14372,6 +14452,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14543,6 +14624,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Le panier craque. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14710,6 +14792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14881,6 +14964,7 @@
           <t>narrateur|Kenzo a choisi la dînette. Un oiseau passe derrière la vitre. Kenzo range la dînette miniature. Il demande à Papa, l'adulte. Les mains attendent, près de Papa. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15072,6 +15156,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15243,6 +15328,7 @@
           <t>narrateur|Kenzo prend une pomme. Le train souffle. Papa dit oui pour une pomme. Kenzo a demandé. L'inconnu, on le demande. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15410,6 +15496,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15581,6 +15668,7 @@
           <t>narrateur|Kenzo prend un yaourt. Le panier craque. Papa dit oui pour un yaourt. Kenzo a demandé à l'adulte. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15748,6 +15836,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15919,6 +16008,7 @@
           <t>narrateur|Kenzo prend un morceau de pain. Un oiseau passe derrière la vitre. Papa dit oui pour un morceau de pain. Les mains attendent, puis remercient. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Les mains attendent. Kenzo dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16086,6 +16176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16104,7 +16195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16128,6 +16219,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16329,6 +16434,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
